--- a/recipes/onion-garlic-free-indian/focus-states/13-karnataka/excel/karnataka-recipes.xlsx
+++ b/recipes/onion-garlic-free-indian/focus-states/13-karnataka/excel/karnataka-recipes.xlsx
@@ -104,7 +104,7 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="009A3412"/>
-      <sz val="16"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="19">
@@ -259,7 +259,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -358,6 +358,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="18" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1465,7 +1468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1477,7 +1480,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Beans Palya</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Beans Palya</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1487,7 +1490,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Karnataka kitchen  ·  Side  ·  Udupi, Mysuru and North Karnataka vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Karnataka  ·  Side</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -1507,44 +1510,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>12 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>22 min</t>
+          <t>Prep 10 min · Cook 12 min</t>
         </is>
       </c>
     </row>
@@ -1746,37 +1749,203 @@
       <c r="C22" s="46" t="n"/>
       <c r="D22" s="46" t="n"/>
     </row>
-    <row r="23" ht="36" customHeight="1">
+    <row r="23" ht="66" customHeight="1">
       <c r="A23" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B23" s="48" t="inlineStr">
         <is>
-          <t>Temper, cook, coconut.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C23" s="49" t="n"/>
       <c r="D23" s="49" t="n"/>
     </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Heat fat in Stainless steel kadhai or saucepan — never aluminium on medium. Bloom hing 20–30 seconds until fragrant — this is the onion-garlic stand-in. Do not burn it.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Temper, cook, coconut. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B27" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables yield to a knife, gravy coats a spoon, salt is balanced. Rest 2 minutes off the heat so seasoning settles.</t>
+        </is>
+      </c>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B28" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C28" s="31" t="n"/>
+      <c r="D28" s="31" t="n"/>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B29" s="48" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C29" s="49" t="n"/>
+      <c r="D29" s="49" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="n"/>
+      <c r="C31" s="22" t="n"/>
+      <c r="D31" s="22" t="n"/>
+    </row>
+    <row r="32" ht="36" customHeight="1">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>kcal 425  ·  Protein 23 g  ·  Carbs 64 g  ·  Fat 10 g  ·  Fibre 19 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B32" s="50" t="n"/>
+      <c r="C32" s="50" t="n"/>
+      <c r="D32" s="50" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+    </row>
+    <row r="34" ht="48" customHeight="1">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Mustard · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="26" t="n"/>
+      <c r="D34" s="26" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n"/>
+      <c r="C35" s="6" t="n"/>
+      <c r="D35" s="6" t="n"/>
+    </row>
+    <row r="36" ht="72" customHeight="1">
+      <c r="A36" s="25" t="inlineStr">
+        <is>
+          <t>For Beans Palya: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B36" s="26" t="n"/>
+      <c r="C36" s="26" t="n"/>
+      <c r="D36" s="26" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B37" s="52" t="n"/>
+      <c r="C37" s="52" t="n"/>
+      <c r="D37" s="52" t="n"/>
+    </row>
+    <row r="38" ht="64" customHeight="1">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>Serve family-style in a steel bowl. Keep a lid on at the pass so it does not skin. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Mustard; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B38" s="50" t="n"/>
+      <c r="C38" s="50" t="n"/>
+      <c r="D38" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="31">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="A21:D21"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="C17:D17"/>
     <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -1790,7 +1959,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1802,7 +1971,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Thondekayi Palya</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Thondekayi Palya</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1812,7 +1981,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Karnataka kitchen  ·  Side  ·  Udupi, Mysuru and North Karnataka vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Karnataka  ·  Side</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -1832,44 +2001,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>Prep 10 min · Cook 15 min</t>
         </is>
       </c>
     </row>
@@ -2035,35 +2204,188 @@
       <c r="C20" s="46" t="n"/>
       <c r="D20" s="46" t="n"/>
     </row>
-    <row r="21" ht="36" customHeight="1">
+    <row r="21" ht="66" customHeight="1">
       <c r="A21" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B21" s="48" t="inlineStr">
         <is>
-          <t>Fry until the gourd is tender-crisp.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C21" s="49" t="n"/>
       <c r="D21" s="49" t="n"/>
     </row>
+    <row r="22" ht="36" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="54" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Fry until the gourd is tender-crisp. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables yield to a knife, gravy coats a spoon, salt is balanced. Rest 2 minutes off the heat so seasoning settles.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="n"/>
+      <c r="C28" s="22" t="n"/>
+      <c r="D28" s="22" t="n"/>
+    </row>
+    <row r="29" ht="36" customHeight="1">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>kcal 181  ·  Protein 4 g  ·  Carbs 18 g  ·  Fat 11 g  ·  Fibre 5 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B29" s="50" t="n"/>
+      <c r="C29" s="50" t="n"/>
+      <c r="D29" s="50" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+    </row>
+    <row r="31" ht="48" customHeight="1">
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>Mustard · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="n"/>
+      <c r="C31" s="26" t="n"/>
+      <c r="D31" s="26" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+    </row>
+    <row r="33" ht="72" customHeight="1">
+      <c r="A33" s="25" t="inlineStr">
+        <is>
+          <t>For Thondekayi Palya: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B33" s="26" t="n"/>
+      <c r="C33" s="26" t="n"/>
+      <c r="D33" s="26" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B34" s="52" t="n"/>
+      <c r="C34" s="52" t="n"/>
+      <c r="D34" s="52" t="n"/>
+    </row>
+    <row r="35" ht="64" customHeight="1">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>Serve family-style in a steel bowl. Keep a lid on at the pass so it does not skin. Service temperature: Hot. Allergen label for this dish: Mustard; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B35" s="50" t="n"/>
+      <c r="C35" s="50" t="n"/>
+      <c r="D35" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="28">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A19:D19"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -2077,7 +2399,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2089,7 +2411,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Palak Palya</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Palak Palya</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2099,7 +2421,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Karnataka kitchen  ·  Side  ·  Udupi, Mysuru and North Karnataka vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Karnataka  ·  Side</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -2119,44 +2441,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>12 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>22 min</t>
+          <t>Prep 10 min · Cook 12 min</t>
         </is>
       </c>
     </row>
@@ -2340,36 +2662,202 @@
       <c r="C21" s="46" t="n"/>
       <c r="D21" s="46" t="n"/>
     </row>
-    <row r="22" ht="36" customHeight="1">
+    <row r="22" ht="66" customHeight="1">
       <c r="A22" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B22" s="48" t="inlineStr">
         <is>
-          <t>Wilt, coconut.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C22" s="49" t="n"/>
       <c r="D22" s="49" t="n"/>
     </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. Wash greens in several changes of water; drain and squeeze dry.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="54" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Heat fat in Stainless steel kadhai or saucepan — never aluminium on medium. Bloom hing 20–30 seconds until fragrant — this is the onion-garlic stand-in. Do not burn it.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Wilt, coconut. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B26" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables yield to a knife, gravy coats a spoon, salt is balanced. Rest 2 minutes off the heat so seasoning settles.</t>
+        </is>
+      </c>
+      <c r="C26" s="49" t="n"/>
+      <c r="D26" s="49" t="n"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B27" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C27" s="31" t="n"/>
+      <c r="D27" s="31" t="n"/>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B28" s="48" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C28" s="49" t="n"/>
+      <c r="D28" s="49" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B30" s="22" t="n"/>
+      <c r="C30" s="22" t="n"/>
+      <c r="D30" s="22" t="n"/>
+    </row>
+    <row r="31" ht="36" customHeight="1">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>kcal 106  ·  Protein 3 g  ·  Carbs 7 g  ·  Fat 9 g  ·  Fibre 4 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B31" s="50" t="n"/>
+      <c r="C31" s="50" t="n"/>
+      <c r="D31" s="50" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+    </row>
+    <row r="33" ht="48" customHeight="1">
+      <c r="A33" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Mustard · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B33" s="26" t="n"/>
+      <c r="C33" s="26" t="n"/>
+      <c r="D33" s="26" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n"/>
+      <c r="C34" s="6" t="n"/>
+      <c r="D34" s="6" t="n"/>
+    </row>
+    <row r="35" ht="72" customHeight="1">
+      <c r="A35" s="25" t="inlineStr">
+        <is>
+          <t>Wash greens until the water is clear; grit ruins the dish. For Palak Palya: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B35" s="26" t="n"/>
+      <c r="C35" s="26" t="n"/>
+      <c r="D35" s="26" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B36" s="52" t="n"/>
+      <c r="C36" s="52" t="n"/>
+      <c r="D36" s="52" t="n"/>
+    </row>
+    <row r="37" ht="64" customHeight="1">
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t>Serve family-style in a steel bowl. Keep a lid on at the pass so it does not skin. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Mustard; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B37" s="50" t="n"/>
+      <c r="C37" s="50" t="n"/>
+      <c r="D37" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="30">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -2383,7 +2871,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2395,7 +2883,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Ragi Roti</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Ragi Roti</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2405,7 +2893,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Karnataka kitchen  ·  Bread  ·  Udupi, Mysuru and North Karnataka vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Karnataka  ·  Bread</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -2425,44 +2913,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>Prep 15 min · Cook 15 min</t>
         </is>
       </c>
     </row>
@@ -2628,35 +3116,188 @@
       <c r="C20" s="46" t="n"/>
       <c r="D20" s="46" t="n"/>
     </row>
-    <row r="21" ht="36" customHeight="1">
+    <row r="21" ht="54" customHeight="1">
       <c r="A21" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B21" s="48" t="inlineStr">
         <is>
-          <t>Pat onto iron tawa.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Cast-iron tawa (not aluminium). Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C21" s="49" t="n"/>
       <c r="D21" s="49" t="n"/>
     </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. For dough, add water gradually; rest covered 10–15 minutes before rolling.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="54" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Pat onto iron tawa. Work in Cast-iron tawa (not aluminium). Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: bread is cooked through, no wet dough in the centre, light brown spots on the face.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Hold wrapped in a clean cloth in a covered steel box up to 30 minutes. Refresh on a hot tawa 20 seconds if needed. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="n"/>
+      <c r="C28" s="22" t="n"/>
+      <c r="D28" s="22" t="n"/>
+    </row>
+    <row r="29" ht="36" customHeight="1">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>kcal 216  ·  Protein 5 g  ·  Carbs 46 g  ·  Fat 1 g  ·  Fibre 7 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B29" s="50" t="n"/>
+      <c r="C29" s="50" t="n"/>
+      <c r="D29" s="50" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+    </row>
+    <row r="31" ht="48" customHeight="1">
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="n"/>
+      <c r="C31" s="26" t="n"/>
+      <c r="D31" s="26" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+    </row>
+    <row r="33" ht="72" customHeight="1">
+      <c r="A33" s="25" t="inlineStr">
+        <is>
+          <t>For Ragi Roti: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B33" s="26" t="n"/>
+      <c r="C33" s="26" t="n"/>
+      <c r="D33" s="26" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B34" s="52" t="n"/>
+      <c r="C34" s="52" t="n"/>
+      <c r="D34" s="52" t="n"/>
+    </row>
+    <row r="35" ht="64" customHeight="1">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>Send to table wrapped. Do not stack in plastic or they sweat. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B35" s="50" t="n"/>
+      <c r="C35" s="50" t="n"/>
+      <c r="D35" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="28">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A19:D19"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -2670,7 +3311,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2682,7 +3323,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Akki Roti</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Akki Roti</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2692,7 +3333,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Karnataka kitchen  ·  Bread  ·  Udupi, Mysuru and North Karnataka vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Karnataka  ·  Bread</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -2712,44 +3353,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>Prep 15 min · Cook 15 min</t>
         </is>
       </c>
     </row>
@@ -2933,36 +3574,189 @@
       <c r="C21" s="46" t="n"/>
       <c r="D21" s="46" t="n"/>
     </row>
-    <row r="22" ht="36" customHeight="1">
+    <row r="22" ht="54" customHeight="1">
       <c r="A22" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B22" s="48" t="inlineStr">
         <is>
-          <t>Pat on banana leaf onto iron tawa.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Cast-iron tawa (not aluminium). Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C22" s="49" t="n"/>
       <c r="D22" s="49" t="n"/>
     </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. For dough, add water gradually; rest covered 10–15 minutes before rolling.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="54" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Pat on banana leaf onto iron tawa. Work in Cast-iron tawa (not aluminium). Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: bread is cooked through, no wet dough in the centre, light brown spots on the face.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B26" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C26" s="49" t="n"/>
+      <c r="D26" s="49" t="n"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B27" s="30" t="inlineStr">
+        <is>
+          <t>Hold wrapped in a clean cloth in a covered steel box up to 30 minutes. Refresh on a hot tawa 20 seconds if needed. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C27" s="31" t="n"/>
+      <c r="D27" s="31" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="n"/>
+      <c r="C29" s="22" t="n"/>
+      <c r="D29" s="22" t="n"/>
+    </row>
+    <row r="30" ht="36" customHeight="1">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>kcal 142  ·  Protein 3 g  ·  Carbs 31 g  ·  Fat 0 g  ·  Fibre 1 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B30" s="50" t="n"/>
+      <c r="C30" s="50" t="n"/>
+      <c r="D30" s="50" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="48" customHeight="1">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="26" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+    </row>
+    <row r="34" ht="72" customHeight="1">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>For Akki Roti: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="26" t="n"/>
+      <c r="D34" s="26" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B35" s="52" t="n"/>
+      <c r="C35" s="52" t="n"/>
+      <c r="D35" s="52" t="n"/>
+    </row>
+    <row r="36" ht="64" customHeight="1">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>Send to table wrapped. Do not stack in plastic or they sweat. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B36" s="50" t="n"/>
+      <c r="C36" s="50" t="n"/>
+      <c r="D36" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="29">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -2976,7 +3770,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2988,7 +3782,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Neer Dosa</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Neer Dosa</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2998,7 +3792,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Karnataka kitchen  ·  Bread  ·  Udupi, Mysuru and North Karnataka vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Karnataka  ·  Bread</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -3018,44 +3812,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>Prep 20 min · Cook 15 min</t>
         </is>
       </c>
     </row>
@@ -3167,32 +3961,211 @@
       <c r="C17" s="46" t="n"/>
       <c r="D17" s="46" t="n"/>
     </row>
-    <row r="18" ht="36" customHeight="1">
+    <row r="18" ht="54" customHeight="1">
       <c r="A18" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B18" s="48" t="inlineStr">
         <is>
-          <t>Pour on hot iron tawa. Do not spread like regular dosa. Fold.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Cast-iron tawa (not aluminium). Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C18" s="49" t="n"/>
       <c r="D18" s="49" t="n"/>
     </row>
+    <row r="19" ht="42" customHeight="1">
+      <c r="A19" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B19" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. For dough, add water gradually; rest covered 10–15 minutes before rolling.</t>
+        </is>
+      </c>
+      <c r="C19" s="31" t="n"/>
+      <c r="D19" s="31" t="n"/>
+    </row>
+    <row r="20" ht="54" customHeight="1">
+      <c r="A20" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B20" s="48" t="inlineStr">
+        <is>
+          <t>Pour on hot iron tawa. Work in Cast-iron tawa (not aluminium). Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C20" s="49" t="n"/>
+      <c r="D20" s="49" t="n"/>
+    </row>
+    <row r="21" ht="54" customHeight="1">
+      <c r="A21" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B21" s="30" t="inlineStr">
+        <is>
+          <t>Do not spread like regular dosa. Work in Cast-iron tawa (not aluminium). Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C21" s="31" t="n"/>
+      <c r="D21" s="31" t="n"/>
+    </row>
+    <row r="22" ht="54" customHeight="1">
+      <c r="A22" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B22" s="48" t="inlineStr">
+        <is>
+          <t>Fold. Work in Cast-iron tawa (not aluminium). Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C22" s="49" t="n"/>
+      <c r="D22" s="49" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: bread is cooked through, no wet dough in the centre, light brown spots on the face.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Hold wrapped in a clean cloth in a covered steel box up to 30 minutes. Refresh on a hot tawa 20 seconds if needed. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="n"/>
+      <c r="C27" s="22" t="n"/>
+      <c r="D27" s="22" t="n"/>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>kcal 180  ·  Protein 4 g  ·  Carbs 40 g  ·  Fat 0 g  ·  Fibre 1 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B28" s="50" t="n"/>
+      <c r="C28" s="50" t="n"/>
+      <c r="D28" s="50" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+    </row>
+    <row r="30" ht="48" customHeight="1">
+      <c r="A30" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B30" s="26" t="n"/>
+      <c r="C30" s="26" t="n"/>
+      <c r="D30" s="26" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="72" customHeight="1">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>For Neer Dosa: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="26" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B33" s="52" t="n"/>
+      <c r="C33" s="52" t="n"/>
+      <c r="D33" s="52" t="n"/>
+    </row>
+    <row r="34" ht="64" customHeight="1">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>Send to table wrapped. Do not stack in plastic or they sweat. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B34" s="50" t="n"/>
+      <c r="C34" s="50" t="n"/>
+      <c r="D34" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="27">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="B17:D17"/>
     <mergeCell ref="B18:D18"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -3206,7 +4179,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3218,7 +4191,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Mysore Pak</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Mysore Pak</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3228,7 +4201,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Karnataka kitchen  ·  Sweet  ·  Udupi, Mysuru and North Karnataka vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Karnataka  ·  Sweet</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -3248,44 +4221,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>Prep 10 min · Cook 20 min</t>
         </is>
       </c>
     </row>
@@ -3415,33 +4388,186 @@
       <c r="C18" s="46" t="n"/>
       <c r="D18" s="46" t="n"/>
     </row>
-    <row r="19" ht="36" customHeight="1">
+    <row r="19" ht="66" customHeight="1">
       <c r="A19" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B19" s="48" t="inlineStr">
         <is>
-          <t>Cook in steel, pour into a steel tray.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C19" s="49" t="n"/>
       <c r="D19" s="49" t="n"/>
     </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B20" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C20" s="31" t="n"/>
+      <c r="D20" s="31" t="n"/>
+    </row>
+    <row r="21" ht="54" customHeight="1">
+      <c r="A21" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B21" s="48" t="inlineStr">
+        <is>
+          <t>Cook in steel, pour into a steel tray. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C21" s="49" t="n"/>
+      <c r="D21" s="49" t="n"/>
+    </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: mixture leaves the sides of the pan, or milk is thick enough to coat a spoon, or syrup has taken the stated string.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Hold as the dish is eaten — hot sweets in a bain of hot water, chilled sweets in the fridge. Label date and time. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="n"/>
+      <c r="C26" s="22" t="n"/>
+      <c r="D26" s="22" t="n"/>
+    </row>
+    <row r="27" ht="36" customHeight="1">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>kcal 450  ·  Protein 8 g  ·  Carbs 84 g  ·  Fat 9 g  ·  Fibre 4 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B27" s="50" t="n"/>
+      <c r="C27" s="50" t="n"/>
+      <c r="D27" s="50" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6" t="n"/>
+    </row>
+    <row r="29" ht="48" customHeight="1">
+      <c r="A29" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B29" s="26" t="n"/>
+      <c r="C29" s="26" t="n"/>
+      <c r="D29" s="26" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+    </row>
+    <row r="31" ht="72" customHeight="1">
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>For Mysore Pak: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder. Cook or roast besan until the raw smell is gone.</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="n"/>
+      <c r="C31" s="26" t="n"/>
+      <c r="D31" s="26" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B32" s="52" t="n"/>
+      <c r="C32" s="52" t="n"/>
+      <c r="D32" s="52" t="n"/>
+    </row>
+    <row r="33" ht="64" customHeight="1">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>Cut even portions. Garnish with nuts only if the allergen card allows. Service temperature: Hot. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B33" s="50" t="n"/>
+      <c r="C33" s="50" t="n"/>
+      <c r="D33" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="26">
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A26:D26"/>
     <mergeCell ref="B18:D18"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -3455,7 +4581,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3467,7 +4593,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Obbattu / Holige</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Obbattu / Holige</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3477,7 +4603,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Karnataka kitchen  ·  Sweet  ·  Udupi, Mysuru and North Karnataka vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Karnataka  ·  Sweet</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -3497,44 +4623,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>40 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>65 min</t>
+          <t>Prep 40 min · Cook 25 min</t>
         </is>
       </c>
     </row>
@@ -3646,32 +4772,185 @@
       <c r="C17" s="46" t="n"/>
       <c r="D17" s="46" t="n"/>
     </row>
-    <row r="18" ht="36" customHeight="1">
+    <row r="18" ht="54" customHeight="1">
       <c r="A18" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B18" s="48" t="inlineStr">
         <is>
-          <t>Stuff, roll thin, cook on iron with ghee.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Cast-iron tawa (not aluminium). Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C18" s="49" t="n"/>
       <c r="D18" s="49" t="n"/>
     </row>
+    <row r="19" ht="36" customHeight="1">
+      <c r="A19" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B19" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C19" s="31" t="n"/>
+      <c r="D19" s="31" t="n"/>
+    </row>
+    <row r="20" ht="54" customHeight="1">
+      <c r="A20" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B20" s="48" t="inlineStr">
+        <is>
+          <t>Stuff, roll thin, cook on iron with ghee. Work in Cast-iron tawa (not aluminium). Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C20" s="49" t="n"/>
+      <c r="D20" s="49" t="n"/>
+    </row>
+    <row r="21" ht="42" customHeight="1">
+      <c r="A21" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B21" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: mixture leaves the sides of the pan, or milk is thick enough to coat a spoon, or syrup has taken the stated string.</t>
+        </is>
+      </c>
+      <c r="C21" s="31" t="n"/>
+      <c r="D21" s="31" t="n"/>
+    </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B22" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C22" s="49" t="n"/>
+      <c r="D22" s="49" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Hold as the dish is eaten — hot sweets in a bain of hot water, chilled sweets in the fridge. Label date and time. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="n"/>
+      <c r="C25" s="22" t="n"/>
+      <c r="D25" s="22" t="n"/>
+    </row>
+    <row r="26" ht="36" customHeight="1">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>kcal 452  ·  Protein 18 g  ·  Carbs 86 g  ·  Fat 4 g  ·  Fibre 12 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B26" s="50" t="n"/>
+      <c r="C26" s="50" t="n"/>
+      <c r="D26" s="50" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n"/>
+      <c r="C27" s="6" t="n"/>
+      <c r="D27" s="6" t="n"/>
+    </row>
+    <row r="28" ht="48" customHeight="1">
+      <c r="A28" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B28" s="26" t="n"/>
+      <c r="C28" s="26" t="n"/>
+      <c r="D28" s="26" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+    </row>
+    <row r="30" ht="72" customHeight="1">
+      <c r="A30" s="25" t="inlineStr">
+        <is>
+          <t>For Obbattu / Holige: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B30" s="26" t="n"/>
+      <c r="C30" s="26" t="n"/>
+      <c r="D30" s="26" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B31" s="52" t="n"/>
+      <c r="C31" s="52" t="n"/>
+      <c r="D31" s="52" t="n"/>
+    </row>
+    <row r="32" ht="64" customHeight="1">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>Cut even portions. Garnish with nuts only if the allergen card allows. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B32" s="50" t="n"/>
+      <c r="C32" s="50" t="n"/>
+      <c r="D32" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="25">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="A26:D26"/>
     <mergeCell ref="B18:D18"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -3685,7 +4964,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3697,7 +4976,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Dharwad Peda</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Dharwad Peda</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3707,7 +4986,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Karnataka kitchen  ·  Sweet  ·  Udupi, Mysuru and North Karnataka vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Karnataka  ·  Sweet</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -3727,44 +5006,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>40 min</t>
+          <t>Prep 15 min · Cook 25 min</t>
         </is>
       </c>
     </row>
@@ -3894,33 +5173,186 @@
       <c r="C18" s="46" t="n"/>
       <c r="D18" s="46" t="n"/>
     </row>
-    <row r="19" ht="36" customHeight="1">
+    <row r="19" ht="66" customHeight="1">
       <c r="A19" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B19" s="48" t="inlineStr">
         <is>
-          <t>Slow-cook khoya in steel until brown, shape pedas.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C19" s="49" t="n"/>
       <c r="D19" s="49" t="n"/>
     </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B20" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C20" s="31" t="n"/>
+      <c r="D20" s="31" t="n"/>
+    </row>
+    <row r="21" ht="66" customHeight="1">
+      <c r="A21" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B21" s="48" t="inlineStr">
+        <is>
+          <t>Slow-cook khoya in steel until brown, shape pedas. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C21" s="49" t="n"/>
+      <c r="D21" s="49" t="n"/>
+    </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: mixture leaves the sides of the pan, or milk is thick enough to coat a spoon, or syrup has taken the stated string.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Hold as the dish is eaten — hot sweets in a bain of hot water, chilled sweets in the fridge. Label date and time. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="n"/>
+      <c r="C26" s="22" t="n"/>
+      <c r="D26" s="22" t="n"/>
+    </row>
+    <row r="27" ht="36" customHeight="1">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>kcal 308  ·  Protein 7 g  ·  Carbs 38 g  ·  Fat 13 g  ·  Fibre 0 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B27" s="50" t="n"/>
+      <c r="C27" s="50" t="n"/>
+      <c r="D27" s="50" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6" t="n"/>
+    </row>
+    <row r="29" ht="48" customHeight="1">
+      <c r="A29" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B29" s="26" t="n"/>
+      <c r="C29" s="26" t="n"/>
+      <c r="D29" s="26" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+    </row>
+    <row r="31" ht="72" customHeight="1">
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>For Dharwad Peda: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="n"/>
+      <c r="C31" s="26" t="n"/>
+      <c r="D31" s="26" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B32" s="52" t="n"/>
+      <c r="C32" s="52" t="n"/>
+      <c r="D32" s="52" t="n"/>
+    </row>
+    <row r="33" ht="64" customHeight="1">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>Cut even portions. Garnish with nuts only if the allergen card allows. Service temperature: Hot. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B33" s="50" t="n"/>
+      <c r="C33" s="50" t="n"/>
+      <c r="D33" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="26">
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A26:D26"/>
     <mergeCell ref="B18:D18"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -3934,7 +5366,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3946,7 +5378,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Moong Dal Payasa</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Moong Dal Payasa</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3956,7 +5388,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Karnataka kitchen  ·  Dessert  ·  Udupi, Mysuru and North Karnataka vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Karnataka  ·  Dessert</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -3976,44 +5408,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>40 min</t>
+          <t>Prep 10 min · Cook 30 min</t>
         </is>
       </c>
     </row>
@@ -4179,35 +5611,201 @@
       <c r="C20" s="46" t="n"/>
       <c r="D20" s="46" t="n"/>
     </row>
-    <row r="21" ht="36" customHeight="1">
+    <row r="21" ht="66" customHeight="1">
       <c r="A21" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B21" s="48" t="inlineStr">
         <is>
-          <t>Cook dal, jaggery, coconut milk. Do not boil hard.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C21" s="49" t="n"/>
       <c r="D21" s="49" t="n"/>
     </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. Use a heavy stainless steel milk pot. Acidic or milk dishes must never touch aluminium.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="54" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Cook dal, jaggery, coconut milk. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="54" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Do not boil hard. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: mixture leaves the sides of the pan, or milk is thick enough to coat a spoon, or syrup has taken the stated string.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B27" s="48" t="inlineStr">
+        <is>
+          <t>Hold as the dish is eaten — hot sweets in a bain of hot water, chilled sweets in the fridge. Label date and time. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="n"/>
+      <c r="C29" s="22" t="n"/>
+      <c r="D29" s="22" t="n"/>
+    </row>
+    <row r="30" ht="36" customHeight="1">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>kcal 608  ·  Protein 13 g  ·  Carbs 65 g  ·  Fat 36 g  ·  Fibre 15 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B30" s="50" t="n"/>
+      <c r="C30" s="50" t="n"/>
+      <c r="D30" s="50" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="48" customHeight="1">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="26" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+    </row>
+    <row r="34" ht="72" customHeight="1">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>For Moong Dal Payasa: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="26" t="n"/>
+      <c r="D34" s="26" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B35" s="52" t="n"/>
+      <c r="C35" s="52" t="n"/>
+      <c r="D35" s="52" t="n"/>
+    </row>
+    <row r="36" ht="64" customHeight="1">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>Serve in steel or glass bowls. If chilled, take out 5 minutes before the pass. Service temperature: Hot. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B36" s="50" t="n"/>
+      <c r="C36" s="50" t="n"/>
+      <c r="D36" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="29">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A19:D19"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -4485,7 +6083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4497,7 +6095,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Chiroti with Badam Milk</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Chiroti with Badam Milk</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4507,7 +6105,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Karnataka kitchen  ·  Dessert  ·  Udupi, Mysuru and North Karnataka vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Karnataka  ·  Dessert</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -4527,44 +6125,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>45 min</t>
+          <t>Prep 25 min · Cook 20 min</t>
         </is>
       </c>
     </row>
@@ -4694,33 +6292,199 @@
       <c r="C18" s="46" t="n"/>
       <c r="D18" s="46" t="n"/>
     </row>
-    <row r="19" ht="36" customHeight="1">
+    <row r="19" ht="66" customHeight="1">
       <c r="A19" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B19" s="48" t="inlineStr">
         <is>
-          <t>Fry chiroti in steel. Serve soaking in warm almond milk.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Steel kadhai for frying — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C19" s="49" t="n"/>
       <c r="D19" s="49" t="n"/>
     </row>
+    <row r="20" ht="42" customHeight="1">
+      <c r="A20" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B20" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. Use a heavy stainless steel milk pot. Acidic or milk dishes must never touch aluminium.</t>
+        </is>
+      </c>
+      <c r="C20" s="31" t="n"/>
+      <c r="D20" s="31" t="n"/>
+    </row>
+    <row r="21" ht="54" customHeight="1">
+      <c r="A21" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B21" s="48" t="inlineStr">
+        <is>
+          <t>Fry chiroti in steel. Work in Steel kadhai for frying — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C21" s="49" t="n"/>
+      <c r="D21" s="49" t="n"/>
+    </row>
+    <row r="22" ht="54" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Serve soaking in warm almond milk. Work in Steel kadhai for frying — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: mixture leaves the sides of the pan, or milk is thick enough to coat a spoon, or syrup has taken the stated string.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Hold as the dish is eaten — hot sweets in a bain of hot water, chilled sweets in the fridge. Label date and time. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="n"/>
+      <c r="C27" s="22" t="n"/>
+      <c r="D27" s="22" t="n"/>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>kcal 404  ·  Protein 10 g  ·  Carbs 79 g  ·  Fat 5 g  ·  Fibre 2 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B28" s="50" t="n"/>
+      <c r="C28" s="50" t="n"/>
+      <c r="D28" s="50" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+    </row>
+    <row r="30" ht="48" customHeight="1">
+      <c r="A30" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Milk · Tree nuts · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B30" s="26" t="n"/>
+      <c r="C30" s="26" t="n"/>
+      <c r="D30" s="26" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="72" customHeight="1">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>For Chiroti with Badam Milk: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="26" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B33" s="52" t="n"/>
+      <c r="C33" s="52" t="n"/>
+      <c r="D33" s="52" t="n"/>
+    </row>
+    <row r="34" ht="64" customHeight="1">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>Serve in steel or glass bowls. If chilled, take out 5 minutes before the pass. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Milk; Tree nuts; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B34" s="50" t="n"/>
+      <c r="C34" s="50" t="n"/>
+      <c r="D34" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="27">
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="B18:D18"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -4734,7 +6498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4746,7 +6510,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Rice Payasa</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Rice Payasa</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4756,7 +6520,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Karnataka kitchen  ·  Dessert  ·  Udupi, Mysuru and North Karnataka vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Karnataka  ·  Dessert</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -4776,44 +6540,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>45 min</t>
+          <t>Prep 10 min · Cook 35 min</t>
         </is>
       </c>
     </row>
@@ -4961,34 +6725,187 @@
       <c r="C19" s="46" t="n"/>
       <c r="D19" s="46" t="n"/>
     </row>
-    <row r="20" ht="36" customHeight="1">
+    <row r="20" ht="66" customHeight="1">
       <c r="A20" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B20" s="48" t="inlineStr">
         <is>
-          <t>Simmer in steel.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Heavy stainless steel milk pot — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C20" s="49" t="n"/>
       <c r="D20" s="49" t="n"/>
     </row>
+    <row r="21" ht="42" customHeight="1">
+      <c r="A21" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. Use a heavy stainless steel milk pot. Acidic or milk dishes must never touch aluminium.</t>
+        </is>
+      </c>
+      <c r="C21" s="31" t="n"/>
+      <c r="D21" s="31" t="n"/>
+    </row>
+    <row r="22" ht="54" customHeight="1">
+      <c r="A22" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B22" s="48" t="inlineStr">
+        <is>
+          <t>Simmer in steel. Work in Heavy stainless steel milk pot — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C22" s="49" t="n"/>
+      <c r="D22" s="49" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: mixture leaves the sides of the pan, or milk is thick enough to coat a spoon, or syrup has taken the stated string.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Hold as the dish is eaten — hot sweets in a bain of hot water, chilled sweets in the fridge. Label date and time. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="n"/>
+      <c r="C27" s="22" t="n"/>
+      <c r="D27" s="22" t="n"/>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>kcal 436  ·  Protein 12 g  ·  Carbs 77 g  ·  Fat 9 g  ·  Fibre 1 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B28" s="50" t="n"/>
+      <c r="C28" s="50" t="n"/>
+      <c r="D28" s="50" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+    </row>
+    <row r="30" ht="48" customHeight="1">
+      <c r="A30" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B30" s="26" t="n"/>
+      <c r="C30" s="26" t="n"/>
+      <c r="D30" s="26" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="72" customHeight="1">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>For Rice Payasa: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="26" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B33" s="52" t="n"/>
+      <c r="C33" s="52" t="n"/>
+      <c r="D33" s="52" t="n"/>
+    </row>
+    <row r="34" ht="64" customHeight="1">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>Serve in steel or glass bowls. If chilled, take out 5 minutes before the pass. Service temperature: Hot. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B34" s="50" t="n"/>
+      <c r="C34" s="50" t="n"/>
+      <c r="D34" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="27">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B25:D25"/>
     <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -5002,7 +6919,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5014,7 +6931,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Moong Kosambari</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Moong Kosambari</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5024,7 +6941,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Karnataka kitchen  ·  Salad  ·  Udupi, Mysuru and North Karnataka vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Karnataka  ·  Salad</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -5044,44 +6961,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>2 min</t>
+          <t>Cold</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>32 min</t>
+          <t>Prep 30 min · Cook 2 min</t>
         </is>
       </c>
     </row>
@@ -5265,36 +7182,202 @@
       <c r="C21" s="46" t="n"/>
       <c r="D21" s="46" t="n"/>
     </row>
-    <row r="22" ht="36" customHeight="1">
+    <row r="22" ht="54" customHeight="1">
       <c r="A22" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B22" s="48" t="inlineStr">
         <is>
-          <t>Mix, temper. Festival salad, already sattvic.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Steel or glass bowl. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C22" s="49" t="n"/>
       <c r="D22" s="49" t="n"/>
     </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="54" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Mix, temper. Work in Steel or glass bowl. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Festival salad, already sattvic. Work in Steel or glass bowl. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B26" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables stay crisp; dressing coats evenly; seasoning is bright, not flat.</t>
+        </is>
+      </c>
+      <c r="C26" s="49" t="n"/>
+      <c r="D26" s="49" t="n"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B27" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C27" s="31" t="n"/>
+      <c r="D27" s="31" t="n"/>
+    </row>
+    <row r="28" ht="54" customHeight="1">
+      <c r="A28" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B28" s="48" t="inlineStr">
+        <is>
+          <t>Hold chilled, covered, up to 2 hours. Stir before service. Discard if it weeps heavily or smells sour beyond yogurt character. Service: Cold.</t>
+        </is>
+      </c>
+      <c r="C28" s="49" t="n"/>
+      <c r="D28" s="49" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B30" s="22" t="n"/>
+      <c r="C30" s="22" t="n"/>
+      <c r="D30" s="22" t="n"/>
+    </row>
+    <row r="31" ht="36" customHeight="1">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>kcal 233  ·  Protein 10 g  ·  Carbs 31 g  ·  Fat 9 g  ·  Fibre 9 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B31" s="50" t="n"/>
+      <c r="C31" s="50" t="n"/>
+      <c r="D31" s="50" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+    </row>
+    <row r="33" ht="48" customHeight="1">
+      <c r="A33" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Mustard · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B33" s="26" t="n"/>
+      <c r="C33" s="26" t="n"/>
+      <c r="D33" s="26" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n"/>
+      <c r="C34" s="6" t="n"/>
+      <c r="D34" s="6" t="n"/>
+    </row>
+    <row r="35" ht="72" customHeight="1">
+      <c r="A35" s="25" t="inlineStr">
+        <is>
+          <t>For Moong Kosambari: squeeze wet vegetables dry or the bowl weeps on the pass. Season slightly higher than you think — cold dulls salt. No onion, no garlic, no allium garnish. Use steel or glass, never aluminium. Dress at the last minute. Verify dahi and spice labels.</t>
+        </is>
+      </c>
+      <c r="B35" s="26" t="n"/>
+      <c r="C35" s="26" t="n"/>
+      <c r="D35" s="26" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B36" s="52" t="n"/>
+      <c r="C36" s="52" t="n"/>
+      <c r="D36" s="52" t="n"/>
+    </row>
+    <row r="37" ht="64" customHeight="1">
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t>Dress at the last minute. Toss at the pass, do not send a wet bowl. Service temperature: Cold. Allergen label for this dish: Milk; Mustard; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B37" s="50" t="n"/>
+      <c r="C37" s="50" t="n"/>
+      <c r="D37" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="30">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -5308,7 +7391,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5320,7 +7403,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Carrot Kosambari</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Carrot Kosambari</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5330,7 +7413,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Karnataka kitchen  ·  Salad  ·  Udupi, Mysuru and North Karnataka vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Karnataka  ·  Salad</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -5350,44 +7433,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>2 min</t>
+          <t>Cold</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>17 min</t>
+          <t>Prep 15 min · Cook 2 min</t>
         </is>
       </c>
     </row>
@@ -5571,36 +7654,189 @@
       <c r="C21" s="46" t="n"/>
       <c r="D21" s="46" t="n"/>
     </row>
-    <row r="22" ht="36" customHeight="1">
+    <row r="22" ht="54" customHeight="1">
       <c r="A22" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B22" s="48" t="inlineStr">
         <is>
-          <t>Mix, temper.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Steel or glass bowl. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C22" s="49" t="n"/>
       <c r="D22" s="49" t="n"/>
     </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="54" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Mix, temper. Work in Steel or glass bowl. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables stay crisp; dressing coats evenly; seasoning is bright, not flat.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B26" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C26" s="49" t="n"/>
+      <c r="D26" s="49" t="n"/>
+    </row>
+    <row r="27" ht="54" customHeight="1">
+      <c r="A27" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B27" s="30" t="inlineStr">
+        <is>
+          <t>Hold chilled, covered, up to 2 hours. Stir before service. Discard if it weeps heavily or smells sour beyond yogurt character. Service: Cold.</t>
+        </is>
+      </c>
+      <c r="C27" s="31" t="n"/>
+      <c r="D27" s="31" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="n"/>
+      <c r="C29" s="22" t="n"/>
+      <c r="D29" s="22" t="n"/>
+    </row>
+    <row r="30" ht="36" customHeight="1">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>kcal 240  ·  Protein 10 g  ·  Carbs 33 g  ·  Fat 9 g  ·  Fibre 10 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B30" s="50" t="n"/>
+      <c r="C30" s="50" t="n"/>
+      <c r="D30" s="50" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="48" customHeight="1">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Mustard · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="26" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+    </row>
+    <row r="34" ht="72" customHeight="1">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>For Carrot Kosambari: squeeze wet vegetables dry or the bowl weeps on the pass. Season slightly higher than you think — cold dulls salt. No onion, no garlic, no allium garnish. Use steel or glass, never aluminium. Dress at the last minute. Verify dahi and spice labels.</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="26" t="n"/>
+      <c r="D34" s="26" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B35" s="52" t="n"/>
+      <c r="C35" s="52" t="n"/>
+      <c r="D35" s="52" t="n"/>
+    </row>
+    <row r="36" ht="64" customHeight="1">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>Dress at the last minute. Toss at the pass, do not send a wet bowl. Service temperature: Cold. Allergen label for this dish: Milk; Mustard; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B36" s="50" t="n"/>
+      <c r="C36" s="50" t="n"/>
+      <c r="D36" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="29">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -5614,7 +7850,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5626,7 +7862,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Tomato Gojju Relish</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Tomato Gojju Relish</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5636,7 +7872,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Karnataka kitchen  ·  Salad  ·  Udupi, Mysuru and North Karnataka vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Karnataka  ·  Salad</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -5656,44 +7892,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>12 min</t>
+          <t>Cold</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>22 min</t>
+          <t>Prep 10 min · Cook 12 min</t>
         </is>
       </c>
     </row>
@@ -5895,37 +8131,216 @@
       <c r="C22" s="46" t="n"/>
       <c r="D22" s="46" t="n"/>
     </row>
-    <row r="23" ht="36" customHeight="1">
+    <row r="23" ht="66" customHeight="1">
       <c r="A23" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B23" s="48" t="inlineStr">
         <is>
-          <t>Cook to a relish. No onion.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C23" s="49" t="n"/>
       <c r="D23" s="49" t="n"/>
     </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Heat fat in Stainless steel kadhai or saucepan — never aluminium on medium. Bloom hing 20–30 seconds until fragrant — this is the onion-garlic stand-in. Do not burn it.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Cook to a relish. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="54" customHeight="1">
+      <c r="A27" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B27" s="48" t="inlineStr">
+        <is>
+          <t>No onion. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B28" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables stay crisp; dressing coats evenly; seasoning is bright, not flat.</t>
+        </is>
+      </c>
+      <c r="C28" s="31" t="n"/>
+      <c r="D28" s="31" t="n"/>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B29" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C29" s="49" t="n"/>
+      <c r="D29" s="49" t="n"/>
+    </row>
+    <row r="30" ht="54" customHeight="1">
+      <c r="A30" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B30" s="30" t="inlineStr">
+        <is>
+          <t>Hold chilled, covered, up to 2 hours. Stir before service. Discard if it weeps heavily or smells sour beyond yogurt character. Service: Cold.</t>
+        </is>
+      </c>
+      <c r="C30" s="31" t="n"/>
+      <c r="D30" s="31" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B32" s="22" t="n"/>
+      <c r="C32" s="22" t="n"/>
+      <c r="D32" s="22" t="n"/>
+    </row>
+    <row r="33" ht="36" customHeight="1">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>kcal 114  ·  Protein 1 g  ·  Carbs 28 g  ·  Fat 0 g  ·  Fibre 1 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B33" s="50" t="n"/>
+      <c r="C33" s="50" t="n"/>
+      <c r="D33" s="50" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n"/>
+      <c r="C34" s="6" t="n"/>
+      <c r="D34" s="6" t="n"/>
+    </row>
+    <row r="35" ht="48" customHeight="1">
+      <c r="A35" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Milk · Mustard · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B35" s="26" t="n"/>
+      <c r="C35" s="26" t="n"/>
+      <c r="D35" s="26" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="n"/>
+      <c r="C36" s="6" t="n"/>
+      <c r="D36" s="6" t="n"/>
+    </row>
+    <row r="37" ht="72" customHeight="1">
+      <c r="A37" s="25" t="inlineStr">
+        <is>
+          <t>For Tomato Gojju Relish: squeeze wet vegetables dry or the bowl weeps on the pass. Season slightly higher than you think — cold dulls salt. No onion, no garlic, no allium garnish. Use steel or glass, never aluminium. Dress at the last minute. Verify dahi and spice labels.</t>
+        </is>
+      </c>
+      <c r="B37" s="26" t="n"/>
+      <c r="C37" s="26" t="n"/>
+      <c r="D37" s="26" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B38" s="52" t="n"/>
+      <c r="C38" s="52" t="n"/>
+      <c r="D38" s="52" t="n"/>
+    </row>
+    <row r="39" ht="64" customHeight="1">
+      <c r="A39" s="12" t="inlineStr">
+        <is>
+          <t>Dress at the last minute. Toss at the pass, do not send a wet bowl. Service temperature: Cold. Allergen label for this dish: Gluten (wheat); Milk; Mustard; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B39" s="50" t="n"/>
+      <c r="C39" s="50" t="n"/>
+      <c r="D39" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="32">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="A21:D21"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="C17:D17"/>
     <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -9218,7 +11633,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9230,7 +11645,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Maddur Vada</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Maddur Vada</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9240,7 +11655,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Karnataka kitchen  ·  Starter  ·  Udupi, Mysuru and North Karnataka vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Karnataka  ·  Starter</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -9260,44 +11675,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>Prep 20 min · Cook 15 min</t>
         </is>
       </c>
     </row>
@@ -9535,39 +11950,205 @@
       <c r="C24" s="46" t="n"/>
       <c r="D24" s="46" t="n"/>
     </row>
-    <row r="25" ht="36" customHeight="1">
+    <row r="25" ht="66" customHeight="1">
       <c r="A25" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B25" s="48" t="inlineStr">
         <is>
-          <t>Flatten thin, fry crisp in steel.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Steel kadhai for frying — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C25" s="49" t="n"/>
       <c r="D25" s="49" t="n"/>
     </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. For dough, add water gradually; rest covered 10–15 minutes before rolling.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="54" customHeight="1">
+      <c r="A27" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B27" s="48" t="inlineStr">
+        <is>
+          <t>Heat fat in Steel kadhai for frying — never aluminium on medium. Bloom hing 20–30 seconds until fragrant — this is the onion-garlic stand-in. Do not burn it.</t>
+        </is>
+      </c>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+    </row>
+    <row r="28" ht="54" customHeight="1">
+      <c r="A28" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B28" s="30" t="inlineStr">
+        <is>
+          <t>Flatten thin, fry crisp in steel. Work in Steel kadhai for frying — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C28" s="31" t="n"/>
+      <c r="D28" s="31" t="n"/>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B29" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: crust or crumb is set, centre is hot, no raw flour or potato taste. Drain on a steel rack, not paper in the fryer basket.</t>
+        </is>
+      </c>
+      <c r="C29" s="49" t="n"/>
+      <c r="D29" s="49" t="n"/>
+    </row>
+    <row r="30" ht="42" customHeight="1">
+      <c r="A30" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B30" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C30" s="31" t="n"/>
+      <c r="D30" s="31" t="n"/>
+    </row>
+    <row r="31" ht="42" customHeight="1">
+      <c r="A31" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B31" s="48" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C31" s="49" t="n"/>
+      <c r="D31" s="49" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B33" s="22" t="n"/>
+      <c r="C33" s="22" t="n"/>
+      <c r="D33" s="22" t="n"/>
+    </row>
+    <row r="34" ht="36" customHeight="1">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>kcal 589  ·  Protein 14 g  ·  Carbs 95 g  ·  Fat 18 g  ·  Fibre 12 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B34" s="50" t="n"/>
+      <c r="C34" s="50" t="n"/>
+      <c r="D34" s="50" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n"/>
+      <c r="C35" s="6" t="n"/>
+      <c r="D35" s="6" t="n"/>
+    </row>
+    <row r="36" ht="48" customHeight="1">
+      <c r="A36" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B36" s="26" t="n"/>
+      <c r="C36" s="26" t="n"/>
+      <c r="D36" s="26" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="n"/>
+      <c r="C37" s="6" t="n"/>
+      <c r="D37" s="6" t="n"/>
+    </row>
+    <row r="38" ht="72" customHeight="1">
+      <c r="A38" s="25" t="inlineStr">
+        <is>
+          <t>For Maddur Vada: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B38" s="26" t="n"/>
+      <c r="C38" s="26" t="n"/>
+      <c r="D38" s="26" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B39" s="52" t="n"/>
+      <c r="C39" s="52" t="n"/>
+      <c r="D39" s="52" t="n"/>
+    </row>
+    <row r="40" ht="64" customHeight="1">
+      <c r="A40" s="12" t="inlineStr">
+        <is>
+          <t>Serve immediately while crisp or hot. Offer a chutney or raita that is also onion-garlic free. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B40" s="50" t="n"/>
+      <c r="C40" s="50" t="n"/>
+      <c r="D40" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="33">
     <mergeCell ref="A23:D23"/>
     <mergeCell ref="A8:D8"/>
     <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A38:D38"/>
     <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B29:D29"/>
     <mergeCell ref="C20:D20"/>
+    <mergeCell ref="B28:D28"/>
     <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A40:D40"/>
     <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="B30:D30"/>
     <mergeCell ref="A11:D11"/>
     <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
     <mergeCell ref="C21:D21"/>
+    <mergeCell ref="B26:D26"/>
     <mergeCell ref="B25:D25"/>
     <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="B31:D31"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="C19:D19"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A33:D33"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -9581,7 +12162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9593,7 +12174,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Goli Baje</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Goli Baje</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9603,7 +12184,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Karnataka kitchen  ·  Starter  ·  Udupi, Mysuru and North Karnataka vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Karnataka  ·  Starter</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -9623,44 +12204,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>Prep 15 min · Cook 15 min</t>
         </is>
       </c>
     </row>
@@ -9862,37 +12443,216 @@
       <c r="C22" s="46" t="n"/>
       <c r="D22" s="46" t="n"/>
     </row>
-    <row r="23" ht="36" customHeight="1">
+    <row r="23" ht="66" customHeight="1">
       <c r="A23" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B23" s="48" t="inlineStr">
         <is>
-          <t>Drop blobs, fry. Serve with coconut chutney (no garlic).</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Steel kadhai for frying — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C23" s="49" t="n"/>
       <c r="D23" s="49" t="n"/>
     </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Heat fat in Steel kadhai for frying — never aluminium on medium. Bloom hing 20–30 seconds until fragrant — this is the onion-garlic stand-in. Do not burn it.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Drop blobs, fry. Work in Steel kadhai for frying — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="54" customHeight="1">
+      <c r="A27" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B27" s="48" t="inlineStr">
+        <is>
+          <t>Serve with coconut chutney (no garlic). Work in Steel kadhai for frying — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B28" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: crust or crumb is set, centre is hot, no raw flour or potato taste. Drain on a steel rack, not paper in the fryer basket.</t>
+        </is>
+      </c>
+      <c r="C28" s="31" t="n"/>
+      <c r="D28" s="31" t="n"/>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B29" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C29" s="49" t="n"/>
+      <c r="D29" s="49" t="n"/>
+    </row>
+    <row r="30" ht="42" customHeight="1">
+      <c r="A30" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B30" s="30" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C30" s="31" t="n"/>
+      <c r="D30" s="31" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B32" s="22" t="n"/>
+      <c r="C32" s="22" t="n"/>
+      <c r="D32" s="22" t="n"/>
+    </row>
+    <row r="33" ht="36" customHeight="1">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>kcal 324  ·  Protein 8 g  ·  Carbs 51 g  ·  Fat 9 g  ·  Fibre 2 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B33" s="50" t="n"/>
+      <c r="C33" s="50" t="n"/>
+      <c r="D33" s="50" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n"/>
+      <c r="C34" s="6" t="n"/>
+      <c r="D34" s="6" t="n"/>
+    </row>
+    <row r="35" ht="48" customHeight="1">
+      <c r="A35" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B35" s="26" t="n"/>
+      <c r="C35" s="26" t="n"/>
+      <c r="D35" s="26" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="n"/>
+      <c r="C36" s="6" t="n"/>
+      <c r="D36" s="6" t="n"/>
+    </row>
+    <row r="37" ht="72" customHeight="1">
+      <c r="A37" s="25" t="inlineStr">
+        <is>
+          <t>For Goli Baje: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder. Bring yogurt to a simmer gently and stir; a rolling boil can split it.</t>
+        </is>
+      </c>
+      <c r="B37" s="26" t="n"/>
+      <c r="C37" s="26" t="n"/>
+      <c r="D37" s="26" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B38" s="52" t="n"/>
+      <c r="C38" s="52" t="n"/>
+      <c r="D38" s="52" t="n"/>
+    </row>
+    <row r="39" ht="64" customHeight="1">
+      <c r="A39" s="12" t="inlineStr">
+        <is>
+          <t>Serve immediately while crisp or hot. Offer a chutney or raita that is also onion-garlic free. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B39" s="50" t="n"/>
+      <c r="C39" s="50" t="n"/>
+      <c r="D39" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="32">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="A21:D21"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="C17:D17"/>
     <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -9906,7 +12666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9918,7 +12678,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Mangalore Buns</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Mangalore Buns</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9928,7 +12688,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Karnataka kitchen  ·  Starter  ·  Udupi, Mysuru and North Karnataka vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Karnataka  ·  Starter</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -9948,44 +12708,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>80 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>95 min</t>
+          <t>Prep 80 min · Cook 15 min</t>
         </is>
       </c>
     </row>
@@ -10169,36 +12929,189 @@
       <c r="C21" s="46" t="n"/>
       <c r="D21" s="46" t="n"/>
     </row>
-    <row r="22" ht="36" customHeight="1">
+    <row r="22" ht="66" customHeight="1">
       <c r="A22" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B22" s="48" t="inlineStr">
         <is>
-          <t>Rest dough, roll thick, fry in steel until they puff.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Steel kadhai for frying — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C22" s="49" t="n"/>
       <c r="D22" s="49" t="n"/>
     </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="54" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Rest dough, roll thick, fry in steel until they puff. Work in Steel kadhai for frying — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: crust or crumb is set, centre is hot, no raw flour or potato taste. Drain on a steel rack, not paper in the fryer basket.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B26" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C26" s="49" t="n"/>
+      <c r="D26" s="49" t="n"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B27" s="30" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C27" s="31" t="n"/>
+      <c r="D27" s="31" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="n"/>
+      <c r="C29" s="22" t="n"/>
+      <c r="D29" s="22" t="n"/>
+    </row>
+    <row r="30" ht="36" customHeight="1">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>kcal 470  ·  Protein 9 g  ·  Carbs 89 g  ·  Fat 9 g  ·  Fibre 3 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B30" s="50" t="n"/>
+      <c r="C30" s="50" t="n"/>
+      <c r="D30" s="50" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="48" customHeight="1">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="26" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+    </row>
+    <row r="34" ht="72" customHeight="1">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>For Mangalore Buns: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder. Bring yogurt to a simmer gently and stir; a rolling boil can split it.</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="26" t="n"/>
+      <c r="D34" s="26" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B35" s="52" t="n"/>
+      <c r="C35" s="52" t="n"/>
+      <c r="D35" s="52" t="n"/>
+    </row>
+    <row r="36" ht="64" customHeight="1">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>Serve immediately while crisp or hot. Offer a chutney or raita that is also onion-garlic free. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B36" s="50" t="n"/>
+      <c r="C36" s="50" t="n"/>
+      <c r="D36" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="29">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -10212,7 +13125,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10224,7 +13137,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Bisi Bele Bath</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Bisi Bele Bath</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10234,7 +13147,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Karnataka kitchen  ·  Main  ·  Udupi, Mysuru and North Karnataka vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Karnataka  ·  Main</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -10254,44 +13167,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>40 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>60 min</t>
+          <t>Prep 20 min · Cook 40 min</t>
         </is>
       </c>
     </row>
@@ -10547,40 +13460,219 @@
       <c r="C25" s="46" t="n"/>
       <c r="D25" s="46" t="n"/>
     </row>
-    <row r="26" ht="36" customHeight="1">
+    <row r="26" ht="66" customHeight="1">
       <c r="A26" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B26" s="48" t="inlineStr">
         <is>
-          <t>Cook loose and hot. Temple style — no onion, no garlic.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel or clay pot — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C26" s="49" t="n"/>
       <c r="D26" s="49" t="n"/>
     </row>
+    <row r="27" ht="36" customHeight="1">
+      <c r="A27" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B27" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C27" s="31" t="n"/>
+      <c r="D27" s="31" t="n"/>
+    </row>
+    <row r="28" ht="54" customHeight="1">
+      <c r="A28" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B28" s="48" t="inlineStr">
+        <is>
+          <t>Heat fat in Stainless steel or clay pot — never aluminium on medium. Bloom hing 20–30 seconds until fragrant — this is the onion-garlic stand-in. Do not burn it.</t>
+        </is>
+      </c>
+      <c r="C28" s="49" t="n"/>
+      <c r="D28" s="49" t="n"/>
+    </row>
+    <row r="29" ht="54" customHeight="1">
+      <c r="A29" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B29" s="30" t="inlineStr">
+        <is>
+          <t>Cook loose and hot. Work in Stainless steel or clay pot — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C29" s="31" t="n"/>
+      <c r="D29" s="31" t="n"/>
+    </row>
+    <row r="30" ht="54" customHeight="1">
+      <c r="A30" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B30" s="48" t="inlineStr">
+        <is>
+          <t>Temple style — no onion, no garlic. Work in Stainless steel or clay pot — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C30" s="49" t="n"/>
+      <c r="D30" s="49" t="n"/>
+    </row>
+    <row r="31" ht="42" customHeight="1">
+      <c r="A31" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B31" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables yield to a knife, gravy coats a spoon, salt is balanced. Rest 2 minutes off the heat so seasoning settles.</t>
+        </is>
+      </c>
+      <c r="C31" s="31" t="n"/>
+      <c r="D31" s="31" t="n"/>
+    </row>
+    <row r="32" ht="42" customHeight="1">
+      <c r="A32" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B32" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C32" s="49" t="n"/>
+      <c r="D32" s="49" t="n"/>
+    </row>
+    <row r="33" ht="42" customHeight="1">
+      <c r="A33" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B33" s="30" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C33" s="31" t="n"/>
+      <c r="D33" s="31" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B35" s="22" t="n"/>
+      <c r="C35" s="22" t="n"/>
+      <c r="D35" s="22" t="n"/>
+    </row>
+    <row r="36" ht="36" customHeight="1">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>kcal 527  ·  Protein 17 g  ·  Carbs 84 g  ·  Fat 14 g  ·  Fibre 10 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B36" s="50" t="n"/>
+      <c r="C36" s="50" t="n"/>
+      <c r="D36" s="50" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="n"/>
+      <c r="C37" s="6" t="n"/>
+      <c r="D37" s="6" t="n"/>
+    </row>
+    <row r="38" ht="48" customHeight="1">
+      <c r="A38" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Milk · Mustard · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B38" s="26" t="n"/>
+      <c r="C38" s="26" t="n"/>
+      <c r="D38" s="26" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="n"/>
+      <c r="C39" s="6" t="n"/>
+      <c r="D39" s="6" t="n"/>
+    </row>
+    <row r="40" ht="72" customHeight="1">
+      <c r="A40" s="25" t="inlineStr">
+        <is>
+          <t>For Bisi Bele Bath: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B40" s="26" t="n"/>
+      <c r="C40" s="26" t="n"/>
+      <c r="D40" s="26" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B41" s="52" t="n"/>
+      <c r="C41" s="52" t="n"/>
+      <c r="D41" s="52" t="n"/>
+    </row>
+    <row r="42" ht="64" customHeight="1">
+      <c r="A42" s="12" t="inlineStr">
+        <is>
+          <t>Plate with bread or rice from the same kitchen card. Sauce should nap, not flood. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Milk; Mustard; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B42" s="50" t="n"/>
+      <c r="C42" s="50" t="n"/>
+      <c r="D42" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="35">
     <mergeCell ref="A8:D8"/>
     <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A38:D38"/>
     <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B29:D29"/>
     <mergeCell ref="C20:D20"/>
+    <mergeCell ref="B28:D28"/>
     <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A40:D40"/>
     <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A39:D39"/>
     <mergeCell ref="C22:D22"/>
     <mergeCell ref="A24:D24"/>
     <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="B33:D33"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
     <mergeCell ref="C21:D21"/>
+    <mergeCell ref="B32:D32"/>
     <mergeCell ref="B26:D26"/>
+    <mergeCell ref="A41:D41"/>
     <mergeCell ref="B25:D25"/>
     <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="B31:D31"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="C19:D19"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A42:D42"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -10594,7 +13686,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10606,7 +13698,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Saaru Anna</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Saaru Anna</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10616,7 +13708,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Karnataka kitchen  ·  Main  ·  Udupi, Mysuru and North Karnataka vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Karnataka  ·  Main</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -10636,44 +13728,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>45 min</t>
+          <t>Prep 15 min · Cook 30 min</t>
         </is>
       </c>
     </row>
@@ -10911,39 +14003,205 @@
       <c r="C24" s="46" t="n"/>
       <c r="D24" s="46" t="n"/>
     </row>
-    <row r="25" ht="36" customHeight="1">
+    <row r="25" ht="66" customHeight="1">
       <c r="A25" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B25" s="48" t="inlineStr">
         <is>
-          <t>Boil rasam, tadka, pour over hot rice.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel or clay pot — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C25" s="49" t="n"/>
       <c r="D25" s="49" t="n"/>
     </row>
+    <row r="26" ht="36" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="54" customHeight="1">
+      <c r="A27" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B27" s="48" t="inlineStr">
+        <is>
+          <t>Heat fat in Stainless steel or clay pot — never aluminium on medium. Bloom hing 20–30 seconds until fragrant — this is the onion-garlic stand-in. Do not burn it.</t>
+        </is>
+      </c>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+    </row>
+    <row r="28" ht="54" customHeight="1">
+      <c r="A28" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B28" s="30" t="inlineStr">
+        <is>
+          <t>Boil rasam, tadka, pour over hot rice. Work in Stainless steel or clay pot — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C28" s="31" t="n"/>
+      <c r="D28" s="31" t="n"/>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B29" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables yield to a knife, gravy coats a spoon, salt is balanced. Rest 2 minutes off the heat so seasoning settles.</t>
+        </is>
+      </c>
+      <c r="C29" s="49" t="n"/>
+      <c r="D29" s="49" t="n"/>
+    </row>
+    <row r="30" ht="42" customHeight="1">
+      <c r="A30" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B30" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C30" s="31" t="n"/>
+      <c r="D30" s="31" t="n"/>
+    </row>
+    <row r="31" ht="42" customHeight="1">
+      <c r="A31" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B31" s="48" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C31" s="49" t="n"/>
+      <c r="D31" s="49" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B33" s="22" t="n"/>
+      <c r="C33" s="22" t="n"/>
+      <c r="D33" s="22" t="n"/>
+    </row>
+    <row r="34" ht="36" customHeight="1">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>kcal 390  ·  Protein 12 g  ·  Carbs 67 g  ·  Fat 8 g  ·  Fibre 7 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B34" s="50" t="n"/>
+      <c r="C34" s="50" t="n"/>
+      <c r="D34" s="50" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n"/>
+      <c r="C35" s="6" t="n"/>
+      <c r="D35" s="6" t="n"/>
+    </row>
+    <row r="36" ht="48" customHeight="1">
+      <c r="A36" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Milk · Mustard · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B36" s="26" t="n"/>
+      <c r="C36" s="26" t="n"/>
+      <c r="D36" s="26" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="n"/>
+      <c r="C37" s="6" t="n"/>
+      <c r="D37" s="6" t="n"/>
+    </row>
+    <row r="38" ht="72" customHeight="1">
+      <c r="A38" s="25" t="inlineStr">
+        <is>
+          <t>For Saaru Anna: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B38" s="26" t="n"/>
+      <c r="C38" s="26" t="n"/>
+      <c r="D38" s="26" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B39" s="52" t="n"/>
+      <c r="C39" s="52" t="n"/>
+      <c r="D39" s="52" t="n"/>
+    </row>
+    <row r="40" ht="64" customHeight="1">
+      <c r="A40" s="12" t="inlineStr">
+        <is>
+          <t>Plate with bread or rice from the same kitchen card. Sauce should nap, not flood. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Milk; Mustard; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B40" s="50" t="n"/>
+      <c r="C40" s="50" t="n"/>
+      <c r="D40" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="33">
     <mergeCell ref="A23:D23"/>
     <mergeCell ref="A8:D8"/>
     <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A38:D38"/>
     <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B29:D29"/>
     <mergeCell ref="C20:D20"/>
+    <mergeCell ref="B28:D28"/>
     <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A40:D40"/>
     <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="B30:D30"/>
     <mergeCell ref="A11:D11"/>
     <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
     <mergeCell ref="C21:D21"/>
+    <mergeCell ref="B26:D26"/>
     <mergeCell ref="B25:D25"/>
     <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="B31:D31"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="C19:D19"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A33:D33"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -10957,7 +14215,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10969,7 +14227,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Vegetable Huli</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Vegetable Huli</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10979,7 +14237,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Karnataka kitchen  ·  Main  ·  Udupi, Mysuru and North Karnataka vegetarian</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Karnataka  ·  Main</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -10999,44 +14257,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>45 min</t>
+          <t>Prep 15 min · Cook 30 min</t>
         </is>
       </c>
     </row>
@@ -11238,37 +14496,229 @@
       <c r="C22" s="46" t="n"/>
       <c r="D22" s="46" t="n"/>
     </row>
-    <row r="23" ht="36" customHeight="1">
+    <row r="23" ht="66" customHeight="1">
       <c r="A23" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B23" s="48" t="inlineStr">
         <is>
-          <t>Cook veg and dal. Add coconut paste. Temper.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C23" s="49" t="n"/>
       <c r="D23" s="49" t="n"/>
     </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Heat fat in Stainless steel kadhai or saucepan — never aluminium on medium. Bloom hing 20–30 seconds until fragrant — this is the onion-garlic stand-in. Do not burn it.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Cook veg and dal. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="54" customHeight="1">
+      <c r="A27" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B27" s="48" t="inlineStr">
+        <is>
+          <t>Add coconut paste. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+    </row>
+    <row r="28" ht="54" customHeight="1">
+      <c r="A28" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B28" s="30" t="inlineStr">
+        <is>
+          <t>Temper. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C28" s="31" t="n"/>
+      <c r="D28" s="31" t="n"/>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B29" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables yield to a knife, gravy coats a spoon, salt is balanced. Rest 2 minutes off the heat so seasoning settles.</t>
+        </is>
+      </c>
+      <c r="C29" s="49" t="n"/>
+      <c r="D29" s="49" t="n"/>
+    </row>
+    <row r="30" ht="42" customHeight="1">
+      <c r="A30" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B30" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C30" s="31" t="n"/>
+      <c r="D30" s="31" t="n"/>
+    </row>
+    <row r="31" ht="42" customHeight="1">
+      <c r="A31" s="47" t="n">
+        <v>9</v>
+      </c>
+      <c r="B31" s="48" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C31" s="49" t="n"/>
+      <c r="D31" s="49" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B33" s="22" t="n"/>
+      <c r="C33" s="22" t="n"/>
+      <c r="D33" s="22" t="n"/>
+    </row>
+    <row r="34" ht="36" customHeight="1">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>kcal 327  ·  Protein 13 g  ·  Carbs 46 g  ·  Fat 11 g  ·  Fibre 11 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B34" s="50" t="n"/>
+      <c r="C34" s="50" t="n"/>
+      <c r="D34" s="50" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n"/>
+      <c r="C35" s="6" t="n"/>
+      <c r="D35" s="6" t="n"/>
+    </row>
+    <row r="36" ht="48" customHeight="1">
+      <c r="A36" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Mustard · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B36" s="26" t="n"/>
+      <c r="C36" s="26" t="n"/>
+      <c r="D36" s="26" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="n"/>
+      <c r="C37" s="6" t="n"/>
+      <c r="D37" s="6" t="n"/>
+    </row>
+    <row r="38" ht="72" customHeight="1">
+      <c r="A38" s="25" t="inlineStr">
+        <is>
+          <t>For Vegetable Huli: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B38" s="26" t="n"/>
+      <c r="C38" s="26" t="n"/>
+      <c r="D38" s="26" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B39" s="52" t="n"/>
+      <c r="C39" s="52" t="n"/>
+      <c r="D39" s="52" t="n"/>
+    </row>
+    <row r="40" ht="64" customHeight="1">
+      <c r="A40" s="12" t="inlineStr">
+        <is>
+          <t>Plate with bread or rice from the same kitchen card. Sauce should nap, not flood. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Mustard; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B40" s="50" t="n"/>
+      <c r="C40" s="50" t="n"/>
+      <c r="D40" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="33">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="B31:D31"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="A21:D21"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="C17:D17"/>
     <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A33:D33"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
